--- a/data/trans_bre/P2A_fisi_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_fisi_R-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 1,61</t>
+          <t>-6,8; 1,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 4,52</t>
+          <t>-3,6; 4,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 7,5</t>
+          <t>-3,54; 7,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 1,82</t>
+          <t>-4,55; 1,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 5,7</t>
+          <t>-3,28; 4,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 3,76</t>
+          <t>-5,43; 4,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 3,37</t>
+          <t>-2,91; 3,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 2,74</t>
+          <t>-6,57; 2,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-88,12; 218,05</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 3,03</t>
+          <t>-4,87; 2,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,25; 1,57</t>
+          <t>-9,04; 1,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 5,54</t>
+          <t>-7,15; 5,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 7,78</t>
+          <t>-7,29; 7,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-82,24; 444,27</t>
+          <t>-84,75; 367,26</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-6,13; -0,53</t>
+          <t>-5,58; -0,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 2,57</t>
+          <t>-4,11; 2,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 3,25</t>
+          <t>-2,42; 3,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 0,92</t>
+          <t>-9,59; 1,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 40,94</t>
+          <t>-100,0; 55,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-83,24; 160,04</t>
+          <t>-85,3; 147,08</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-72,62; 301,28</t>
+          <t>-71,21; 348,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-81,65; 33,78</t>
+          <t>-78,59; 30,98</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 4,67</t>
+          <t>-6,91; 4,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 4,36</t>
+          <t>-5,26; 3,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 5,23</t>
+          <t>-2,41; 5,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 9,46</t>
+          <t>-2,73; 8,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-85,48; 208,55</t>
+          <t>-87,75; 142,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-82,97; 401,31</t>
+          <t>-88,86; 252,56</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 670,3</t>
+          <t>-83,01; 723,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-32,16; 211,83</t>
+          <t>-34,23; 186,25</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 0,67</t>
+          <t>-6,79; 0,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 6,96</t>
+          <t>-6,22; 6,41</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 4,69</t>
+          <t>-2,23; 4,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 7,29</t>
+          <t>-9,61; 7,02</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-79,95; 376,44</t>
+          <t>-82,97; 277,59</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-68,67; 167,05</t>
+          <t>-71,22; 158,38</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,22; -0,09</t>
+          <t>-3,27; -0,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 1,15</t>
+          <t>-2,64; 1,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,92</t>
+          <t>-1,06; 2,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 1,07</t>
+          <t>-3,49; 1,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-72,53; 2,19</t>
+          <t>-74,67; -4,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-57,31; 48,12</t>
+          <t>-58,16; 45,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-37,95; 135,89</t>
+          <t>-37,38; 145,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-45,59; 22,46</t>
+          <t>-44,88; 29,6</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2A_fisi_R-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P2A_fisi_R-Clase-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 1,44</t>
+          <t>-7,01; 1,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 4,28</t>
+          <t>-3,6; 3,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 7,34</t>
+          <t>-3,62; 7,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 1,97</t>
+          <t>-4,78; 1,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-95,43; 340,06</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 4,75</t>
+          <t>-3,51; 4,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 4,06</t>
+          <t>-4,46; 4,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 3,38</t>
+          <t>-2,97; 3,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 2,61</t>
+          <t>-5,79; 3,03</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-84,25; 196,74</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 2,71</t>
+          <t>-4,45; 2,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-9,04; 1,19</t>
+          <t>-8,9; 1,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 5,04</t>
+          <t>-7,87; 5,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 7,11</t>
+          <t>-7,2; 6,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 383,73</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-84,75; 367,26</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,58; -0,29</t>
+          <t>-6,06; -0,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,11; 2,36</t>
+          <t>-3,97; 2,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 3,34</t>
+          <t>-2,67; 3,37</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,59; 1,0</t>
+          <t>-10,79; 0,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 55,69</t>
+          <t>-100,0; 28,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,3; 147,08</t>
+          <t>-84,07; 152,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-71,21; 348,56</t>
+          <t>-76,68; 278,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-78,59; 30,98</t>
+          <t>-80,87; 26,11</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 4,57</t>
+          <t>-6,29; 4,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 3,72</t>
+          <t>-5,1; 3,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 5,02</t>
+          <t>-2,34; 5,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 8,71</t>
+          <t>-2,4; 9,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-87,75; 142,82</t>
+          <t>-84,3; 205,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-88,86; 252,56</t>
+          <t>-86,72; 307,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-83,01; 723,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-34,23; 186,25</t>
+          <t>-28,91; 212,15</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 0,68</t>
+          <t>-6,62; 0,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 6,41</t>
+          <t>-6,29; 6,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 4,13</t>
+          <t>-2,14; 4,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 7,02</t>
+          <t>-9,83; 6,47</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-82,97; 277,59</t>
+          <t>-85,35; 257,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-71,22; 158,38</t>
+          <t>-68,09; 138,82</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,27; -0,22</t>
+          <t>-3,38; -0,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 1,16</t>
+          <t>-2,6; 1,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 2,13</t>
+          <t>-1,14; 1,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 1,31</t>
+          <t>-3,43; 1,58</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-74,67; -4,69</t>
+          <t>-74,83; 0,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-58,16; 45,26</t>
+          <t>-56,69; 44,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-37,38; 145,7</t>
+          <t>-39,21; 144,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-44,88; 29,6</t>
+          <t>-45,62; 36,37</t>
         </is>
       </c>
     </row>
